--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104671_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104671_W24.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.211499999999999</v>
+        <v>8.895200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1747</v>
+        <v>7.8008</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0368</v>
+        <v>1.0944</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0746</v>
+        <v>6.0613</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3621</v>
+        <v>1.3668</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7125</v>
+        <v>4.6945</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9398</v>
+        <v>6.9056</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8356</v>
+        <v>1.8271</v>
       </c>
       <c r="L2" t="n">
-        <v>5.1043</v>
+        <v>5.0784</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8653</v>
+        <v>-0.8442</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0027</v>
+        <v>0.6957</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3115</v>
+        <v>0.3505</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3142</v>
+        <v>0.3452</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2116</v>
+        <v>7.4232</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4943</v>
+        <v>5.6825</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7173</v>
+        <v>1.7407</v>
       </c>
       <c r="G3" t="n">
-        <v>8.885199999999999</v>
+        <v>8.8711</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1645</v>
+        <v>4.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7206</v>
+        <v>4.7175</v>
       </c>
       <c r="J3" t="n">
-        <v>7.7728</v>
+        <v>7.7348</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8199</v>
+        <v>3.7954</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9529</v>
+        <v>3.9394</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1124</v>
+        <v>1.1363</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.859</v>
+        <v>-0.6268</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3025</v>
+        <v>-0.3061</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7972</v>
+        <v>4.8852</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2022</v>
+        <v>4.5162</v>
       </c>
       <c r="F4" t="n">
-        <v>2.595</v>
+        <v>0.369</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1011</v>
+        <v>2.2336</v>
       </c>
       <c r="H4" t="n">
-        <v>1.619</v>
+        <v>0.8931</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4821</v>
+        <v>1.3405</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0982</v>
+        <v>3.4329</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7548</v>
+        <v>0.6927</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3434</v>
+        <v>2.7402</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0028</v>
+        <v>-1.1993</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8641</v>
+        <v>0.2003</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1387</v>
+        <v>-1.3997</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>-0.0509</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2381</v>
+        <v>0.4294</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3919</v>
+        <v>-0.4804</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0582</v>
+        <v>4.4426</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6557</v>
+        <v>2.0104</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4025</v>
+        <v>2.4322</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2337</v>
+        <v>3.1067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8903</v>
+        <v>1.6198</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3434</v>
+        <v>1.4868</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4589</v>
+        <v>2.085</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7029</v>
+        <v>0.7444</v>
       </c>
       <c r="L5" t="n">
-        <v>2.756</v>
+        <v>1.3405</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2252</v>
+        <v>1.0217</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1874</v>
+        <v>0.8754</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4126</v>
+        <v>0.1463</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8825</v>
+        <v>1.2661</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4688</v>
+        <v>1.0636</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4138</v>
+        <v>0.2025</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5074</v>
+        <v>2.6718</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1133</v>
+        <v>4.256</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.606</v>
+        <v>-1.5842</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1051</v>
+        <v>1.0968</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2224</v>
+        <v>1.2098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2214</v>
+        <v>2.1991</v>
       </c>
       <c r="K6" t="n">
-        <v>1.475</v>
+        <v>1.4544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1162</v>
+        <v>-1.1023</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8559</v>
+        <v>0.0302</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2945</v>
+        <v>0.4713</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4386</v>
+        <v>-0.4411</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0638</v>
+        <v>1.0404</v>
       </c>
       <c r="E7" t="n">
-        <v>1.159</v>
+        <v>1.1532</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.1128</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6786</v>
+        <v>-0.6772</v>
       </c>
       <c r="H7" t="n">
-        <v>1.062</v>
+        <v>1.0626</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7406</v>
+        <v>-1.7398</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5631</v>
+        <v>0.5542</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2417</v>
+        <v>-1.2314</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6082</v>
+        <v>0.5794</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5958</v>
+        <v>0.5991</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0124</v>
+        <v>-0.0196</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8208</v>
+        <v>0.7482</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0655</v>
+        <v>-0.1258</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7553</v>
+        <v>0.874</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1772</v>
+        <v>-0.173</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2626</v>
+        <v>-0.2641</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0853</v>
+        <v>0.0911</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1411</v>
+        <v>-0.1605</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3841</v>
+        <v>0.3685</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0362</v>
+        <v>-0.0125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1322</v>
+        <v>0.0593</v>
       </c>
       <c r="T8" t="n">
-        <v>0.248</v>
+        <v>0.0834</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1159</v>
+        <v>-0.024</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1269</v>
+        <v>0.3193</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4171</v>
+        <v>1.5943</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2902</v>
+        <v>-1.275</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2621</v>
+        <v>-0.2557</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3074</v>
+        <v>-0.3019</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0453</v>
+        <v>0.0462</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2004</v>
+        <v>1.1914</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4626</v>
+        <v>-1.4471</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6109</v>
+        <v>-0.425</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3297</v>
+        <v>-0.1418</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2064</v>
+        <v>0.2105</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2279</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0214</v>
+        <v>0.1439</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0388</v>
+        <v>1.0498</v>
       </c>
       <c r="H10" t="n">
-        <v>0.463</v>
+        <v>0.4733</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5758</v>
+        <v>0.5765</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2409</v>
+        <v>0.2294</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4329</v>
+        <v>0.4309</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8204</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8992</v>
+        <v>-0.5027</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4688</v>
+        <v>-0.1628</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4304</v>
+        <v>-0.3399</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5972</v>
+        <v>-0.2902</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1245</v>
+        <v>0.3578</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7217</v>
+        <v>-0.648</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9021</v>
+        <v>-0.8963</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.7268</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6115</v>
+        <v>0.6088</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5135</v>
+        <v>-1.5052</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6025</v>
+        <v>-0.3044</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0938</v>
+        <v>-1.778</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3845</v>
+        <v>-1.2704</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1393</v>
+        <v>-3.1592</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1125</v>
+        <v>-3.1106</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0268</v>
+        <v>-0.0486</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1709</v>
+        <v>-0.2054</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3672</v>
+        <v>1.3394</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9684</v>
+        <v>-2.9538</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5744</v>
+        <v>-1.5658</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.633</v>
+        <v>-0.3033</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5383</v>
+        <v>-0.3022</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1552</v>
+        <v>-2.4651</v>
       </c>
       <c r="E13" t="n">
-        <v>0.451</v>
+        <v>0.2116</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6062</v>
+        <v>-2.6767</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2864</v>
+        <v>-2.2768</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4792</v>
+        <v>-0.4714</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8072</v>
+        <v>-1.8053</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0639</v>
+        <v>0.0585</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3503</v>
+        <v>-2.3353</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8629</v>
+        <v>0.5353</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3871</v>
+        <v>0.1531</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4757</v>
+        <v>0.3823</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.7448</v>
+        <v>26.1031</v>
       </c>
       <c r="E14" t="n">
-        <v>26.9202</v>
+        <v>27.01600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1755</v>
+        <v>-0.9129000000000005</v>
       </c>
       <c r="G14" t="n">
-        <v>14.9928</v>
+        <v>14.9811</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4499</v>
+        <v>6.4614</v>
       </c>
       <c r="I14" t="n">
-        <v>8.542899999999999</v>
+        <v>8.519599999999997</v>
       </c>
       <c r="J14" t="n">
-        <v>24.8589</v>
+        <v>24.6338</v>
       </c>
       <c r="K14" t="n">
-        <v>10.2395</v>
+        <v>10.13</v>
       </c>
       <c r="L14" t="n">
-        <v>14.6195</v>
+        <v>14.5036</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.866299999999999</v>
+        <v>-9.652700000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.789800000000001</v>
+        <v>-3.6687</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.076499999999999</v>
+        <v>-5.9843</v>
       </c>
       <c r="P14" t="n">
-        <v>6.804900000000001</v>
+        <v>6.8289</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.805099999999999</v>
+        <v>-6.8291</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6098</v>
+        <v>13.6578</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6048</v>
+        <v>0.9529000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.603</v>
+        <v>1.9719</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9984999999999997</v>
+        <v>-1.0188</v>
       </c>
       <c r="V14" t="n">
-        <v>3.3421</v>
+        <v>3.3398</v>
       </c>
       <c r="W14" t="n">
-        <v>7.263</v>
+        <v>7.2393</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.9209</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4586</v>
+        <v>0.5046</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8763</v>
+        <v>1.0064</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.4176</v>
+        <v>-0.5018</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8594</v>
+        <v>-0.8845</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5715</v>
+        <v>-0.6573</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4309</v>
+        <v>-0.2272</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9216</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0363</v>
+        <v>-0.0969</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1147</v>
+        <v>0.7436</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.781</v>
+        <v>-1.5312</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4648</v>
+        <v>-0.5604</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3162</v>
+        <v>-0.9708</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5449</v>
+        <v>1.3192</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5425</v>
+        <v>0.5874</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0024</v>
+        <v>0.7319</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1863</v>
+        <v>0.4303</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2203</v>
+        <v>3.9106</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.034</v>
+        <v>-3.4803</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2547</v>
+        <v>-1.8529</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0491</v>
+        <v>0.5688</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3038</v>
+        <v>-2.4217</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4824</v>
+        <v>1.9006</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9626</v>
+        <v>2.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.1194</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7371</v>
+        <v>-3.7535</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9135</v>
+        <v>-1.4511</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-2.3023</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2142</v>
+        <v>0.5108</v>
       </c>
       <c r="T16" t="n">
-        <v>2.099</v>
+        <v>0.6034</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1152</v>
+        <v>-0.0926</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7635</v>
+        <v>0.2578</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6333</v>
+        <v>3.1418</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8698</v>
+        <v>-2.8839</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.2531</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6506999999999999</v>
+        <v>0.0461</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2107</v>
+        <v>-0.2992</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6866</v>
+        <v>1.4649</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0835</v>
+        <v>0.9513</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7701</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.548</v>
+        <v>-1.718</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5672</v>
+        <v>-0.9052</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9808</v>
+        <v>-0.8129</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5588</v>
+        <v>1.2833</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1735</v>
+        <v>1.0426</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3853</v>
+        <v>0.2407</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2781</v>
+        <v>-0.2126</v>
       </c>
       <c r="E18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3901</v>
+        <v>-0.3243</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1626</v>
+        <v>-0.1592</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3198</v>
+        <v>-0.3172</v>
       </c>
       <c r="J18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2503</v>
+        <v>-0.8667</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5034</v>
+        <v>-0.0495</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7469</v>
+        <v>-0.8172</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2459</v>
+        <v>-1.2349</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5959</v>
+        <v>0.6</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8418</v>
+        <v>-1.8349</v>
       </c>
       <c r="J19" t="n">
-        <v>0.707</v>
+        <v>0.6976</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4878</v>
+        <v>-0.4917</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.953</v>
+        <v>-1.9325</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.196</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7748</v>
+        <v>-1.7832</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.106</v>
+        <v>1.4672</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6688</v>
+        <v>-3.2503</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4567</v>
+        <v>-1.229</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.156</v>
+        <v>-0.5651</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3008</v>
+        <v>-0.6639</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2747</v>
+        <v>0.5034</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1039</v>
+        <v>0.3545</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3786</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1821</v>
+        <v>-1.7325</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2599</v>
+        <v>-0.9196</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9222</v>
+        <v>-0.8129</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9324</v>
+        <v>0.0801</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7652</v>
+        <v>0.1019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1673</v>
+        <v>-0.0218</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8079</v>
+        <v>-2.4777</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7842</v>
+        <v>-0.7655</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.592</v>
+        <v>-1.7122</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2267</v>
+        <v>-2.4485</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5524</v>
+        <v>-1.1465</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6743</v>
+        <v>-1.302</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5262</v>
+        <v>-0.2843</v>
       </c>
       <c r="K21" t="n">
-        <v>0.377</v>
+        <v>0.1034</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1493</v>
+        <v>-0.3877</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.753</v>
+        <v>-2.1642</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9294</v>
+        <v>-1.2499</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8236</v>
+        <v>-0.9143</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9421</v>
+        <v>-0.6423</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6079</v>
+        <v>-0.4114</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3342</v>
+        <v>-0.2309</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6711</v>
+        <v>-3.7933</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7436</v>
+        <v>-0.2114</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9274</v>
+        <v>-3.5819</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5245</v>
+        <v>1.5177</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2294</v>
+        <v>-0.2325</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="J22" t="n">
-        <v>5.5532</v>
+        <v>5.5145</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L22" t="n">
-        <v>4.286</v>
+        <v>4.2669</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.0287</v>
+        <v>-3.9968</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.2172</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9784</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>0.1925</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5792</v>
+        <v>-0.268</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8278</v>
+        <v>-4.4418</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8194</v>
+        <v>-4.601</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1592</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3943</v>
+        <v>-3.3983</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.6289</v>
+        <v>-3.6384</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2346</v>
+        <v>0.2401</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0562</v>
+        <v>-3.0696</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.0935</v>
+        <v>-3.1069</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3381</v>
+        <v>-0.3287</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8892</v>
+        <v>-0.4972</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.124</v>
+        <v>0.0327</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.241</v>
+        <v>-5.6893</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9682</v>
+        <v>-0.9831</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2728</v>
+        <v>-4.7062</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.608</v>
+        <v>-2.436</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.241</v>
+        <v>-1.3561</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.367</v>
+        <v>-1.0799</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6267</v>
+        <v>1.5608</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8934</v>
+        <v>0.1239</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2666</v>
+        <v>1.4369</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2347</v>
+        <v>-3.9968</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1344</v>
+        <v>-1.48</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1003</v>
+        <v>-2.5168</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8598</v>
+        <v>-0.7981</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3266</v>
+        <v>-0.04</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5332</v>
+        <v>-0.7581</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3022</v>
+        <v>-6.1031</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.31</v>
+        <v>-2.114</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.9923</v>
+        <v>-3.9891</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4474</v>
+        <v>-2.6024</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3652</v>
+        <v>-0.2385</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0822</v>
+        <v>-2.3639</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5814</v>
+        <v>0.6063</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1314</v>
+        <v>0.8823</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4499</v>
+        <v>-0.276</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.0287</v>
+        <v>-3.2087</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4966</v>
+        <v>-1.1209</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.5321</v>
+        <v>-2.0879</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4012</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3962</v>
+        <v>-0.4441</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.005</v>
+        <v>-0.2843</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.7448</v>
+        <v>-24.175</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1755</v>
+        <v>0.9132000000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-26.9201</v>
+        <v>-25.088</v>
       </c>
       <c r="G26" t="n">
-        <v>-14.9926</v>
+        <v>-14.9811</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.449799999999999</v>
+        <v>-6.461600000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.542799999999998</v>
+        <v>-8.5197</v>
       </c>
       <c r="J26" t="n">
-        <v>9.866200000000001</v>
+        <v>9.6526</v>
       </c>
       <c r="K26" t="n">
-        <v>3.789700000000002</v>
+        <v>3.668499999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>6.076599999999999</v>
+        <v>5.984</v>
       </c>
       <c r="M26" t="n">
-        <v>-24.8589</v>
+        <v>-24.6339</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.2395</v>
+        <v>-10.13</v>
       </c>
       <c r="O26" t="n">
-        <v>-14.6194</v>
+        <v>-14.504</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6098</v>
+        <v>-13.6577</v>
       </c>
       <c r="R26" t="n">
-        <v>6.805099999999999</v>
+        <v>6.8291</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6047000000000003</v>
+        <v>0.9748000000000003</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9982000000000005</v>
+        <v>1.0187</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.603</v>
+        <v>-0.04380000000000006</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.3421</v>
+        <v>-3.3398</v>
       </c>
       <c r="W26" t="n">
-        <v>3.921</v>
+        <v>3.8996</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.263</v>
+        <v>-7.2393</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104671_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104671_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.8995</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104671_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.2393</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
